--- a/sample_data/demo_stock_lote.xlsx
+++ b/sample_data/demo_stock_lote.xlsx
@@ -486,13 +486,13 @@
         <v>300</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46545</v>
+        <v>46547</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46205</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="3">
@@ -520,13 +520,13 @@
         <v>100</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45955</v>
+        <v>45957</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
     </row>
     <row r="4">
@@ -554,13 +554,13 @@
         <v>40</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46605</v>
+        <v>46607</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46250</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="5">
@@ -588,13 +588,13 @@
         <v>200</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46505</v>
+        <v>46507</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="6">
@@ -622,13 +622,13 @@
         <v>50</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46485</v>
+        <v>46487</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="7">
@@ -656,13 +656,13 @@
         <v>30</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45939</v>
+        <v>45941</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
     </row>
     <row r="8">
@@ -690,13 +690,13 @@
         <v>1000</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46635</v>
+        <v>46637</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="9">
@@ -724,13 +724,13 @@
         <v>120</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46555</v>
+        <v>46557</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="10">
@@ -758,13 +758,13 @@
         <v>2000</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>46805</v>
+        <v>46807</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="11">
@@ -792,13 +792,13 @@
         <v>30</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>46805</v>
+        <v>46807</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="12">
@@ -826,13 +826,13 @@
         <v>600</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>46805</v>
+        <v>46807</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="13">
@@ -860,13 +860,13 @@
         <v>800</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>46705</v>
+        <v>46707</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="14">
@@ -894,7 +894,7 @@
         <v>15</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="15">
@@ -922,7 +922,7 @@
         <v>3</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="16">
@@ -950,7 +950,7 @@
         <v>10</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="17">
@@ -978,7 +978,7 @@
         <v>5000</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="18">
@@ -1006,13 +1006,13 @@
         <v>80</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>46525</v>
+        <v>46527</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
     </row>
   </sheetData>
